--- a/Data/Users.xlsx
+++ b/Data/Users.xlsx
@@ -469,7 +469,7 @@
     <x:col min="7" max="7" width="15.282054" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="16.710625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.282054" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10" s="1" customFormat="1">
@@ -565,7 +565,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="J3" s="2">
-        <x:v>45973.411712419</x:v>
+        <x:v>45988.7007121991</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
